--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-16T09:04:28+00:00</t>
+    <t>2024-10-26T11:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:58:28+00:00</t>
+    <t>2024-10-26T12:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:16:12+00:00</t>
+    <t>2024-10-26T12:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:32:55+00:00</t>
+    <t>2024-10-26T13:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:09:27+00:00</t>
+    <t>2024-10-26T13:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T13:28:10+00:00</t>
+    <t>2024-10-26T14:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9631" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9709" uniqueCount="992">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T14:16:20+00:00</t>
+    <t>2024-10-26T14:33:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2019,6 +2019,22 @@
     <t>Patient.address.extension</t>
   </si>
   <si>
+    <t>Patient.address.extension:municipalityCode</t>
+  </si>
+  <si>
+    <t>municipalityCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-address-municipalityCode}
+</t>
+  </si>
+  <si>
+    <t>Address Municipality Code</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
+  </si>
+  <si>
     <t>Patient.address.use</t>
   </si>
   <si>
@@ -2732,6 +2748,9 @@
   </si>
   <si>
     <t>Patient.contact.address.extension</t>
+  </si>
+  <si>
+    <t>Patient.contact.address.extension:municipalityCode</t>
   </si>
   <si>
     <t>Patient.contact.address.use</t>
@@ -3372,7 +3391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ246"/>
+  <dimension ref="A1:AQ248"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="60.9765625" customWidth="true" bestFit="true"/>
@@ -20402,9 +20421,11 @@
         <v>647</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>646</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>648</v>
+      </c>
       <c r="D139" t="s" s="2">
         <v>21</v>
       </c>
@@ -20419,26 +20440,22 @@
         <v>21</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>113</v>
+        <v>649</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O139" t="s" s="2">
         <v>651</v>
       </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>21</v>
       </c>
@@ -20450,7 +20467,7 @@
         <v>21</v>
       </c>
       <c r="T139" t="s" s="2">
-        <v>652</v>
+        <v>21</v>
       </c>
       <c r="U139" t="s" s="2">
         <v>21</v>
@@ -20462,13 +20479,13 @@
         <v>21</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>653</v>
+        <v>21</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>21</v>
@@ -20486,28 +20503,28 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>655</v>
+        <v>166</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>656</v>
+        <v>21</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>484</v>
+        <v>21</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -20516,7 +20533,7 @@
         <v>21</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>657</v>
+        <v>21</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>21</v>
@@ -20524,10 +20541,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20544,7 +20561,7 @@
         <v>21</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>94</v>
@@ -20553,15 +20570,17 @@
         <v>113</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="O140" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>21</v>
       </c>
@@ -20573,7 +20592,7 @@
         <v>21</v>
       </c>
       <c r="T140" t="s" s="2">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="U140" t="s" s="2">
         <v>21</v>
@@ -20588,10 +20607,10 @@
         <v>117</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>21</v>
@@ -20609,7 +20628,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>82</v>
@@ -20624,7 +20643,7 @@
         <v>105</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>21</v>
+        <v>661</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>21</v>
@@ -20639,7 +20658,7 @@
         <v>21</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>21</v>
@@ -20647,10 +20666,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20673,20 +20692,18 @@
         <v>94</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>21</v>
       </c>
@@ -20698,7 +20715,7 @@
         <v>21</v>
       </c>
       <c r="T141" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="U141" t="s" s="2">
         <v>21</v>
@@ -20710,13 +20727,13 @@
         <v>21</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>21</v>
+        <v>668</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>21</v>
+        <v>669</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>21</v>
@@ -20734,7 +20751,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>82</v>
@@ -20749,13 +20766,13 @@
         <v>105</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>673</v>
+        <v>21</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>21</v>
@@ -20764,7 +20781,7 @@
         <v>21</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AQ141" t="s" s="2">
         <v>21</v>
@@ -20772,10 +20789,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20786,7 +20803,7 @@
         <v>82</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>21</v>
@@ -20801,13 +20818,17 @@
         <v>253</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+        <v>674</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
       </c>
@@ -20819,7 +20840,7 @@
         <v>21</v>
       </c>
       <c r="T142" t="s" s="2">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="U142" t="s" s="2">
         <v>21</v>
@@ -20855,13 +20876,13 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>21</v>
@@ -20870,13 +20891,13 @@
         <v>105</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>681</v>
+        <v>492</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -20885,7 +20906,7 @@
         <v>21</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="AQ142" t="s" s="2">
         <v>21</v>
@@ -20893,10 +20914,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20907,7 +20928,7 @@
         <v>82</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>21</v>
@@ -20916,16 +20937,16 @@
         <v>21</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>253</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>596</v>
+        <v>681</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>597</v>
+        <v>682</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -20940,7 +20961,7 @@
         <v>21</v>
       </c>
       <c r="T143" t="s" s="2">
-        <v>21</v>
+        <v>683</v>
       </c>
       <c r="U143" t="s" s="2">
         <v>21</v>
@@ -20976,28 +20997,28 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>156</v>
+        <v>684</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>21</v>
+        <v>685</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>21</v>
+        <v>686</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -21006,7 +21027,7 @@
         <v>21</v>
       </c>
       <c r="AP143" t="s" s="2">
-        <v>21</v>
+        <v>687</v>
       </c>
       <c r="AQ143" t="s" s="2">
         <v>21</v>
@@ -21014,10 +21035,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21028,7 +21049,7 @@
         <v>82</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>21</v>
@@ -21040,13 +21061,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>141</v>
+        <v>596</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>142</v>
+        <v>597</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -21085,29 +21106,31 @@
         <v>21</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AC144" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>21</v>
@@ -21133,14 +21156,12 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>21</v>
       </c>
@@ -21149,7 +21170,7 @@
         <v>82</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>21</v>
@@ -21161,13 +21182,13 @@
         <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>687</v>
+        <v>140</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>688</v>
+        <v>141</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>689</v>
+        <v>142</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -21206,16 +21227,14 @@
         <v>21</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AC145" s="2"/>
       <c r="AD145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF145" t="s" s="2">
         <v>166</v>
@@ -21239,7 +21258,7 @@
         <v>21</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>690</v>
+        <v>21</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>21</v>
@@ -21256,13 +21275,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C146" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>21</v>
@@ -21284,13 +21303,13 @@
         <v>21</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -21362,7 +21381,7 @@
         <v>21</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>21</v>
@@ -21379,13 +21398,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C147" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="D147" t="s" s="2">
         <v>21</v>
@@ -21407,10 +21426,10 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="L147" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="M147" t="s" s="2">
         <v>700</v>
@@ -21505,7 +21524,7 @@
         <v>702</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C148" t="s" s="2">
         <v>703</v>
@@ -21536,7 +21555,7 @@
         <v>705</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -21608,7 +21627,7 @@
         <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>21</v>
+        <v>706</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>21</v>
@@ -21628,9 +21647,11 @@
         <v>707</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C149" s="2"/>
+        <v>689</v>
+      </c>
+      <c r="C149" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="D149" t="s" s="2">
         <v>21</v>
       </c>
@@ -21651,13 +21672,13 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>253</v>
+        <v>709</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -21681,7 +21702,7 @@
         <v>21</v>
       </c>
       <c r="W149" t="s" s="2">
-        <v>710</v>
+        <v>21</v>
       </c>
       <c r="X149" t="s" s="2">
         <v>21</v>
@@ -21708,19 +21729,19 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>606</v>
+        <v>166</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="AK149" t="s" s="2">
         <v>21</v>
@@ -21746,14 +21767,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>712</v>
+        <v>21</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -21769,7 +21790,7 @@
         <v>21</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>253</v>
@@ -21793,17 +21814,17 @@
         <v>21</v>
       </c>
       <c r="T150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W150" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="U150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="X150" t="s" s="2">
         <v>21</v>
       </c>
@@ -21829,7 +21850,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>716</v>
+        <v>606</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -21841,16 +21862,16 @@
         <v>21</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>717</v>
+        <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>718</v>
+        <v>21</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -21859,7 +21880,7 @@
         <v>21</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>719</v>
+        <v>21</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>21</v>
@@ -21867,21 +21888,21 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>21</v>
@@ -21896,14 +21917,12 @@
         <v>253</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>724</v>
-      </c>
+        <v>719</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>21</v>
@@ -21916,7 +21935,7 @@
         <v>21</v>
       </c>
       <c r="T151" t="s" s="2">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="U151" t="s" s="2">
         <v>21</v>
@@ -21952,7 +21971,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -21967,13 +21986,13 @@
         <v>105</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>21</v>
+        <v>722</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
@@ -21982,7 +22001,7 @@
         <v>21</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>21</v>
@@ -21990,21 +22009,21 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>21</v>
@@ -22019,12 +22038,14 @@
         <v>253</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N152" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>729</v>
+      </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>21</v>
@@ -22037,7 +22058,7 @@
         <v>21</v>
       </c>
       <c r="T152" t="s" s="2">
-        <v>21</v>
+        <v>730</v>
       </c>
       <c r="U152" t="s" s="2">
         <v>21</v>
@@ -22073,7 +22094,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22088,13 +22109,13 @@
         <v>105</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>734</v>
+        <v>21</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
@@ -22103,7 +22124,7 @@
         <v>21</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>21</v>
@@ -22111,14 +22132,14 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -22140,10 +22161,10 @@
         <v>253</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -22158,7 +22179,7 @@
         <v>21</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>741</v>
+        <v>21</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>21</v>
@@ -22194,7 +22215,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22209,13 +22230,13 @@
         <v>105</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -22224,7 +22245,7 @@
         <v>21</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>21</v>
@@ -22232,14 +22253,14 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>21</v>
+        <v>743</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -22261,14 +22282,12 @@
         <v>253</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>749</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>21</v>
@@ -22281,7 +22300,7 @@
         <v>21</v>
       </c>
       <c r="T154" t="s" s="2">
-        <v>21</v>
+        <v>746</v>
       </c>
       <c r="U154" t="s" s="2">
         <v>21</v>
@@ -22317,7 +22336,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>82</v>
@@ -22332,13 +22351,13 @@
         <v>105</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AL154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>21</v>
@@ -22347,7 +22366,7 @@
         <v>21</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>21</v>
@@ -22355,10 +22374,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22369,7 +22388,7 @@
         <v>82</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>21</v>
@@ -22381,18 +22400,18 @@
         <v>94</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" t="s" s="2">
-        <v>757</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>21</v>
       </c>
@@ -22404,7 +22423,7 @@
         <v>21</v>
       </c>
       <c r="T155" t="s" s="2">
-        <v>758</v>
+        <v>21</v>
       </c>
       <c r="U155" t="s" s="2">
         <v>21</v>
@@ -22440,7 +22459,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22455,13 +22474,13 @@
         <v>105</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>21</v>
+        <v>756</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>531</v>
+        <v>757</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>21</v>
@@ -22470,7 +22489,7 @@
         <v>21</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>21</v>
@@ -22478,10 +22497,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22492,7 +22511,7 @@
         <v>82</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>21</v>
@@ -22501,20 +22520,20 @@
         <v>21</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>21</v>
@@ -22527,7 +22546,7 @@
         <v>21</v>
       </c>
       <c r="T156" t="s" s="2">
-        <v>21</v>
+        <v>763</v>
       </c>
       <c r="U156" t="s" s="2">
         <v>21</v>
@@ -22539,13 +22558,13 @@
         <v>21</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>765</v>
+        <v>21</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>766</v>
+        <v>21</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>21</v>
@@ -22563,7 +22582,7 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22584,16 +22603,16 @@
         <v>21</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>767</v>
+        <v>531</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>768</v>
+        <v>21</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="AQ156" t="s" s="2">
         <v>21</v>
@@ -22601,10 +22620,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22627,16 +22646,18 @@
         <v>21</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>154</v>
+        <v>767</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>155</v>
+        <v>768</v>
       </c>
       <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
+      <c r="O157" t="s" s="2">
+        <v>769</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>21</v>
       </c>
@@ -22660,13 +22681,13 @@
         <v>21</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>21</v>
+        <v>770</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>21</v>
+        <v>771</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>21</v>
@@ -22684,7 +22705,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>156</v>
+        <v>766</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -22693,10 +22714,10 @@
         <v>93</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>21</v>
@@ -22705,16 +22726,16 @@
         <v>21</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>158</v>
+        <v>772</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>21</v>
+        <v>773</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>21</v>
+        <v>774</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>21</v>
@@ -22722,21 +22743,21 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>21</v>
@@ -22748,17 +22769,15 @@
         <v>21</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>21</v>
@@ -22795,31 +22814,31 @@
         <v>21</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>21</v>
@@ -22845,14 +22864,14 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -22868,23 +22887,21 @@
         <v>21</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>290</v>
+        <v>163</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>21</v>
       </c>
@@ -22920,19 +22937,19 @@
         <v>21</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>293</v>
+        <v>166</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>82</v>
@@ -22944,7 +22961,7 @@
         <v>21</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>21</v>
@@ -22953,7 +22970,7 @@
         <v>21</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>294</v>
+        <v>158</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>21</v>
@@ -22962,7 +22979,7 @@
         <v>21</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>21</v>
@@ -22970,10 +22987,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22984,7 +23001,7 @@
         <v>82</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>21</v>
@@ -22993,19 +23010,23 @@
         <v>21</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>154</v>
+        <v>289</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>21</v>
       </c>
@@ -23053,19 +23074,19 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>21</v>
@@ -23074,7 +23095,7 @@
         <v>21</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>158</v>
+        <v>294</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>21</v>
@@ -23083,7 +23104,7 @@
         <v>21</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="AQ160" t="s" s="2">
         <v>21</v>
@@ -23091,21 +23112,21 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>21</v>
@@ -23117,17 +23138,15 @@
         <v>21</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -23164,31 +23183,31 @@
         <v>21</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>21</v>
@@ -23214,21 +23233,21 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>21</v>
@@ -23237,23 +23256,21 @@
         <v>21</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>302</v>
+        <v>162</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>303</v>
+        <v>163</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>21</v>
       </c>
@@ -23289,40 +23306,40 @@
         <v>21</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>307</v>
+        <v>166</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>776</v>
+        <v>21</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>308</v>
+        <v>158</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>21</v>
@@ -23331,7 +23348,7 @@
         <v>21</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>21</v>
@@ -23339,10 +23356,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23365,18 +23382,20 @@
         <v>94</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O163" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
       </c>
@@ -23424,7 +23443,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -23439,13 +23458,13 @@
         <v>105</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>21</v>
+        <v>781</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>
@@ -23454,7 +23473,7 @@
         <v>21</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>21</v>
@@ -23462,10 +23481,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23488,18 +23507,18 @@
         <v>94</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>113</v>
+        <v>253</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>21</v>
       </c>
@@ -23547,7 +23566,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -23556,19 +23575,19 @@
         <v>93</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>779</v>
+        <v>21</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>21</v>
@@ -23577,7 +23596,7 @@
         <v>21</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>21</v>
@@ -23585,10 +23604,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23611,17 +23630,17 @@
         <v>94</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -23670,7 +23689,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -23685,13 +23704,13 @@
         <v>105</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>21</v>
@@ -23700,7 +23719,7 @@
         <v>21</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>21</v>
@@ -23708,10 +23727,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23734,19 +23753,17 @@
         <v>94</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>338</v>
+        <v>253</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -23795,7 +23812,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>82</v>
@@ -23804,19 +23821,19 @@
         <v>93</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>21</v>
+        <v>786</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>21</v>
@@ -23825,7 +23842,7 @@
         <v>21</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>21</v>
@@ -23833,10 +23850,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23859,19 +23876,19 @@
         <v>94</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>253</v>
+        <v>338</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>21</v>
@@ -23920,7 +23937,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -23941,7 +23958,7 @@
         <v>21</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>21</v>
@@ -23950,7 +23967,7 @@
         <v>21</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>21</v>
@@ -23958,10 +23975,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23981,22 +23998,22 @@
         <v>21</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>785</v>
+        <v>253</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>786</v>
+        <v>348</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>787</v>
+        <v>349</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>788</v>
+        <v>350</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>789</v>
+        <v>351</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>21</v>
@@ -24033,17 +24050,19 @@
         <v>21</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AC168" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>626</v>
+        <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>784</v>
+        <v>352</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -24064,16 +24083,16 @@
         <v>21</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>790</v>
+        <v>353</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>791</v>
+        <v>354</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>21</v>
@@ -24081,14 +24100,12 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>793</v>
-      </c>
+        <v>789</v>
+      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>21</v>
       </c>
@@ -24109,19 +24126,19 @@
         <v>21</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>338</v>
+        <v>790</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>21</v>
@@ -24158,19 +24175,17 @@
         <v>21</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="AC169" s="2"/>
       <c r="AD169" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>21</v>
+        <v>626</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>82</v>
@@ -24185,13 +24200,13 @@
         <v>105</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>21</v>
@@ -24200,7 +24215,7 @@
         <v>158</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="AQ169" t="s" s="2">
         <v>21</v>
@@ -24208,13 +24223,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>21</v>
@@ -24236,19 +24251,19 @@
         <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>796</v>
+        <v>338</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>21</v>
@@ -24297,7 +24312,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>82</v>
@@ -24318,7 +24333,7 @@
         <v>21</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>21</v>
@@ -24327,7 +24342,7 @@
         <v>158</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="AQ170" t="s" s="2">
         <v>21</v>
@@ -24335,12 +24350,14 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="C171" s="2"/>
+        <v>789</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>800</v>
+      </c>
       <c r="D171" t="s" s="2">
         <v>21</v>
       </c>
@@ -24349,7 +24366,7 @@
         <v>82</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>21</v>
@@ -24361,19 +24378,19 @@
         <v>21</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -24422,13 +24439,13 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>21</v>
@@ -24443,16 +24460,16 @@
         <v>21</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>804</v>
+        <v>21</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>158</v>
       </c>
       <c r="AP171" t="s" s="2">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="AQ171" t="s" s="2">
         <v>21</v>
@@ -24460,10 +24477,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24486,19 +24503,19 @@
         <v>21</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="O172" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -24547,7 +24564,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>82</v>
@@ -24559,25 +24576,25 @@
         <v>21</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>812</v>
+        <v>105</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>21</v>
+        <v>809</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>158</v>
       </c>
       <c r="AP172" t="s" s="2">
-        <v>21</v>
+        <v>810</v>
       </c>
       <c r="AQ172" t="s" s="2">
         <v>21</v>
@@ -24585,10 +24602,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24599,7 +24616,7 @@
         <v>82</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>21</v>
@@ -24611,16 +24628,20 @@
         <v>21</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>253</v>
+        <v>812</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>154</v>
+        <v>813</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>814</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>816</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
       </c>
@@ -24668,19 +24689,19 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>156</v>
+        <v>811</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>21</v>
+        <v>817</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>21</v>
@@ -24689,13 +24710,13 @@
         <v>21</v>
       </c>
       <c r="AM173" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO173" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AN173" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO173" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>21</v>
@@ -24706,21 +24727,21 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>21</v>
@@ -24732,17 +24753,15 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>21</v>
@@ -24791,19 +24810,19 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>21</v>
@@ -24829,14 +24848,14 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>817</v>
+        <v>161</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -24849,26 +24868,24 @@
         <v>21</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K175" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>818</v>
+        <v>162</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>819</v>
+        <v>163</v>
       </c>
       <c r="N175" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="O175" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>21</v>
       </c>
@@ -24916,7 +24933,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>820</v>
+        <v>166</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>82</v>
@@ -24937,7 +24954,7 @@
         <v>21</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>21</v>
@@ -24961,7 +24978,7 @@
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>21</v>
+        <v>822</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -24974,23 +24991,25 @@
         <v>21</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="N176" s="2"/>
+        <v>824</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O176" t="s" s="2">
-        <v>824</v>
+        <v>211</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>21</v>
@@ -25015,31 +25034,31 @@
         <v>21</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF176" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>82</v>
@@ -25051,7 +25070,7 @@
         <v>21</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>21</v>
@@ -25060,16 +25079,16 @@
         <v>21</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP176" t="s" s="2">
-        <v>827</v>
+        <v>21</v>
       </c>
       <c r="AQ176" t="s" s="2">
         <v>21</v>
@@ -25077,10 +25096,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25091,7 +25110,7 @@
         <v>82</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>21</v>
@@ -25103,16 +25122,18 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>154</v>
+        <v>827</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>155</v>
+        <v>828</v>
       </c>
       <c r="N177" s="2"/>
-      <c r="O177" s="2"/>
+      <c r="O177" t="s" s="2">
+        <v>829</v>
+      </c>
       <c r="P177" t="s" s="2">
         <v>21</v>
       </c>
@@ -25136,13 +25157,13 @@
         <v>21</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>21</v>
+        <v>830</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>21</v>
+        <v>831</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>21</v>
@@ -25160,19 +25181,19 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>156</v>
+        <v>826</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>21</v>
@@ -25181,16 +25202,16 @@
         <v>21</v>
       </c>
       <c r="AM177" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AN177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO177" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN177" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO177" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AP177" t="s" s="2">
-        <v>21</v>
+        <v>832</v>
       </c>
       <c r="AQ177" t="s" s="2">
         <v>21</v>
@@ -25198,21 +25219,21 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>21</v>
@@ -25224,17 +25245,15 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>21</v>
@@ -25271,31 +25290,31 @@
         <v>21</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>21</v>
@@ -25321,14 +25340,14 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -25344,23 +25363,21 @@
         <v>21</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>290</v>
+        <v>163</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>21</v>
       </c>
@@ -25396,19 +25413,19 @@
         <v>21</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>293</v>
+        <v>166</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>82</v>
@@ -25420,7 +25437,7 @@
         <v>21</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>21</v>
@@ -25429,7 +25446,7 @@
         <v>21</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>294</v>
+        <v>158</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>21</v>
@@ -25438,7 +25455,7 @@
         <v>21</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="AQ179" t="s" s="2">
         <v>21</v>
@@ -25446,10 +25463,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25460,7 +25477,7 @@
         <v>82</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>21</v>
@@ -25469,19 +25486,23 @@
         <v>21</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>154</v>
+        <v>289</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P180" t="s" s="2">
         <v>21</v>
       </c>
@@ -25529,19 +25550,19 @@
         <v>21</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>21</v>
@@ -25550,7 +25571,7 @@
         <v>21</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>158</v>
+        <v>294</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>21</v>
@@ -25559,7 +25580,7 @@
         <v>21</v>
       </c>
       <c r="AP180" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="AQ180" t="s" s="2">
         <v>21</v>
@@ -25567,21 +25588,21 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>21</v>
@@ -25593,17 +25614,15 @@
         <v>21</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>21</v>
@@ -25640,31 +25659,31 @@
         <v>21</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>21</v>
@@ -25690,21 +25709,21 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>21</v>
@@ -25713,23 +25732,21 @@
         <v>21</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>302</v>
+        <v>162</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>303</v>
+        <v>163</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>21</v>
       </c>
@@ -25765,40 +25782,40 @@
         <v>21</v>
       </c>
       <c r="AB182" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AC182" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD182" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE182" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>307</v>
+        <v>166</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>834</v>
+        <v>21</v>
       </c>
       <c r="AL182" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>308</v>
+        <v>158</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>21</v>
@@ -25807,7 +25824,7 @@
         <v>21</v>
       </c>
       <c r="AP182" t="s" s="2">
-        <v>309</v>
+        <v>21</v>
       </c>
       <c r="AQ182" t="s" s="2">
         <v>21</v>
@@ -25815,10 +25832,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25841,18 +25858,20 @@
         <v>94</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O183" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>21</v>
       </c>
@@ -25900,7 +25919,7 @@
         <v>21</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>82</v>
@@ -25915,13 +25934,13 @@
         <v>105</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>21</v>
+        <v>839</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>21</v>
@@ -25930,7 +25949,7 @@
         <v>21</v>
       </c>
       <c r="AP183" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AQ183" t="s" s="2">
         <v>21</v>
@@ -25938,10 +25957,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25964,18 +25983,18 @@
         <v>94</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>113</v>
+        <v>253</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N184" s="2"/>
-      <c r="O184" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>21</v>
       </c>
@@ -26023,7 +26042,7 @@
         <v>21</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>82</v>
@@ -26032,19 +26051,19 @@
         <v>93</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>837</v>
+        <v>21</v>
       </c>
       <c r="AL184" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>21</v>
@@ -26053,7 +26072,7 @@
         <v>21</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AQ184" t="s" s="2">
         <v>21</v>
@@ -26061,10 +26080,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26087,17 +26106,17 @@
         <v>94</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>21</v>
@@ -26146,7 +26165,7 @@
         <v>21</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>82</v>
@@ -26161,13 +26180,13 @@
         <v>105</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="AL185" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>21</v>
@@ -26176,7 +26195,7 @@
         <v>21</v>
       </c>
       <c r="AP185" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="AQ185" t="s" s="2">
         <v>21</v>
@@ -26184,10 +26203,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26210,19 +26229,17 @@
         <v>94</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>338</v>
+        <v>253</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>21</v>
@@ -26271,7 +26288,7 @@
         <v>21</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>82</v>
@@ -26280,19 +26297,19 @@
         <v>93</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>21</v>
+        <v>844</v>
       </c>
       <c r="AL186" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>21</v>
@@ -26301,7 +26318,7 @@
         <v>21</v>
       </c>
       <c r="AP186" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="AQ186" t="s" s="2">
         <v>21</v>
@@ -26309,10 +26326,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26335,19 +26352,19 @@
         <v>94</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>253</v>
+        <v>338</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>21</v>
@@ -26396,7 +26413,7 @@
         <v>21</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>82</v>
@@ -26417,7 +26434,7 @@
         <v>21</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>21</v>
@@ -26426,7 +26443,7 @@
         <v>21</v>
       </c>
       <c r="AP187" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="AQ187" t="s" s="2">
         <v>21</v>
@@ -26434,10 +26451,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26457,20 +26474,22 @@
         <v>21</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>465</v>
+        <v>253</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>843</v>
+        <v>348</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="N188" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O188" t="s" s="2">
-        <v>845</v>
+        <v>351</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>21</v>
@@ -26519,7 +26538,7 @@
         <v>21</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>842</v>
+        <v>352</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>82</v>
@@ -26528,7 +26547,7 @@
         <v>93</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>846</v>
+        <v>21</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>105</v>
@@ -26540,16 +26559,16 @@
         <v>21</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>471</v>
+        <v>353</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP188" t="s" s="2">
-        <v>847</v>
+        <v>354</v>
       </c>
       <c r="AQ188" t="s" s="2">
         <v>21</v>
@@ -26557,10 +26576,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26583,16 +26602,18 @@
         <v>21</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>95</v>
+        <v>465</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>154</v>
+        <v>848</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>155</v>
+        <v>849</v>
       </c>
       <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+      <c r="O189" t="s" s="2">
+        <v>850</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>21</v>
       </c>
@@ -26640,7 +26661,7 @@
         <v>21</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>156</v>
+        <v>847</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>82</v>
@@ -26649,10 +26670,10 @@
         <v>93</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>157</v>
+        <v>851</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>21</v>
@@ -26661,16 +26682,16 @@
         <v>21</v>
       </c>
       <c r="AM189" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN189" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO189" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN189" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AP189" t="s" s="2">
-        <v>21</v>
+        <v>852</v>
       </c>
       <c r="AQ189" t="s" s="2">
         <v>21</v>
@@ -26678,21 +26699,21 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>21</v>
@@ -26704,17 +26725,15 @@
         <v>21</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N190" s="2"/>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
         <v>21</v>
@@ -26751,31 +26770,31 @@
         <v>21</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AC190" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD190" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE190" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>21</v>
@@ -26801,46 +26820,44 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I191" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>477</v>
+        <v>162</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>478</v>
+        <v>163</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>21</v>
       </c>
@@ -26864,43 +26881,43 @@
         <v>21</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>482</v>
+        <v>21</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AC191" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>483</v>
+        <v>166</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>21</v>
@@ -26909,7 +26926,7 @@
         <v>21</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>484</v>
+        <v>158</v>
       </c>
       <c r="AN191" t="s" s="2">
         <v>21</v>
@@ -26918,7 +26935,7 @@
         <v>21</v>
       </c>
       <c r="AP191" t="s" s="2">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="AQ191" t="s" s="2">
         <v>21</v>
@@ -26926,10 +26943,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26946,25 +26963,25 @@
         <v>21</v>
       </c>
       <c r="I192" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J192" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>21</v>
@@ -26989,13 +27006,13 @@
         <v>21</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>21</v>
+        <v>481</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>21</v>
+        <v>482</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>21</v>
@@ -27013,7 +27030,7 @@
         <v>21</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>82</v>
@@ -27034,7 +27051,7 @@
         <v>21</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>21</v>
@@ -27043,7 +27060,7 @@
         <v>21</v>
       </c>
       <c r="AP192" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="AQ192" t="s" s="2">
         <v>21</v>
@@ -27051,14 +27068,14 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>495</v>
+        <v>21</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -27080,15 +27097,17 @@
         <v>253</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O193" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>21</v>
       </c>
@@ -27136,7 +27155,7 @@
         <v>21</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>82</v>
@@ -27151,13 +27170,13 @@
         <v>105</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>853</v>
+        <v>21</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>21</v>
@@ -27166,7 +27185,7 @@
         <v>21</v>
       </c>
       <c r="AP193" t="s" s="2">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="AQ193" t="s" s="2">
         <v>21</v>
@@ -27174,21 +27193,21 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>21</v>
@@ -27203,13 +27222,13 @@
         <v>253</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -27259,13 +27278,13 @@
         <v>21</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>21</v>
@@ -27274,13 +27293,13 @@
         <v>105</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="AN194" t="s" s="2">
         <v>21</v>
@@ -27289,7 +27308,7 @@
         <v>21</v>
       </c>
       <c r="AP194" t="s" s="2">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="AQ194" t="s" s="2">
         <v>21</v>
@@ -27297,14 +27316,14 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>21</v>
+        <v>504</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
@@ -27326,12 +27345,14 @@
         <v>253</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N195" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>21</v>
@@ -27380,7 +27401,7 @@
         <v>21</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>82</v>
@@ -27395,13 +27416,13 @@
         <v>105</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>21</v>
+        <v>860</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="AN195" t="s" s="2">
         <v>21</v>
@@ -27410,7 +27431,7 @@
         <v>21</v>
       </c>
       <c r="AP195" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="AQ195" t="s" s="2">
         <v>21</v>
@@ -27418,10 +27439,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -27447,10 +27468,10 @@
         <v>253</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -27501,7 +27522,7 @@
         <v>21</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>82</v>
@@ -27522,7 +27543,7 @@
         <v>21</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>21</v>
@@ -27531,7 +27552,7 @@
         <v>21</v>
       </c>
       <c r="AP196" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="AQ196" t="s" s="2">
         <v>21</v>
@@ -27539,10 +27560,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27553,7 +27574,7 @@
         <v>82</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>21</v>
@@ -27565,18 +27586,16 @@
         <v>94</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="N197" s="2"/>
-      <c r="O197" t="s" s="2">
-        <v>529</v>
-      </c>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>21</v>
       </c>
@@ -27624,13 +27643,13 @@
         <v>21</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH197" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI197" t="s" s="2">
         <v>21</v>
@@ -27645,7 +27664,7 @@
         <v>21</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="AN197" t="s" s="2">
         <v>21</v>
@@ -27654,7 +27673,7 @@
         <v>21</v>
       </c>
       <c r="AP197" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AQ197" t="s" s="2">
         <v>21</v>
@@ -27662,10 +27681,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27676,7 +27695,7 @@
         <v>82</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>21</v>
@@ -27685,22 +27704,20 @@
         <v>21</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>534</v>
+        <v>196</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>860</v>
+        <v>527</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="N198" t="s" s="2">
-        <v>862</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="N198" s="2"/>
       <c r="O198" t="s" s="2">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="P198" t="s" s="2">
         <v>21</v>
@@ -27749,16 +27766,16 @@
         <v>21</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>859</v>
+        <v>530</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>846</v>
+        <v>21</v>
       </c>
       <c r="AJ198" t="s" s="2">
         <v>105</v>
@@ -27770,16 +27787,16 @@
         <v>21</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="AN198" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP198" t="s" s="2">
-        <v>863</v>
+        <v>532</v>
       </c>
       <c r="AQ198" t="s" s="2">
         <v>21</v>
@@ -27801,7 +27818,7 @@
         <v>82</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>21</v>
@@ -27813,16 +27830,20 @@
         <v>21</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>95</v>
+        <v>534</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>154</v>
+        <v>865</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N199" s="2"/>
-      <c r="O199" s="2"/>
+        <v>866</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="O199" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P199" t="s" s="2">
         <v>21</v>
       </c>
@@ -27870,19 +27891,19 @@
         <v>21</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>156</v>
+        <v>864</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>157</v>
+        <v>851</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>21</v>
@@ -27891,16 +27912,16 @@
         <v>21</v>
       </c>
       <c r="AM199" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AN199" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO199" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AN199" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO199" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AP199" t="s" s="2">
-        <v>21</v>
+        <v>868</v>
       </c>
       <c r="AQ199" t="s" s="2">
         <v>21</v>
@@ -27908,21 +27929,21 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>21</v>
@@ -27934,17 +27955,15 @@
         <v>21</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>21</v>
@@ -27981,31 +28000,31 @@
         <v>21</v>
       </c>
       <c r="AB200" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AC200" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD200" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK200" t="s" s="2">
         <v>21</v>
@@ -28031,21 +28050,21 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>21</v>
@@ -28054,18 +28073,20 @@
         <v>21</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>546</v>
+        <v>162</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N201" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N201" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>21</v>
@@ -28090,52 +28111,52 @@
         <v>21</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>548</v>
+        <v>21</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>549</v>
+        <v>21</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AC201" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD201" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>550</v>
+        <v>166</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>551</v>
+        <v>21</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>867</v>
+        <v>21</v>
       </c>
       <c r="AL201" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>553</v>
+        <v>158</v>
       </c>
       <c r="AN201" t="s" s="2">
         <v>21</v>
@@ -28144,7 +28165,7 @@
         <v>21</v>
       </c>
       <c r="AP201" t="s" s="2">
-        <v>554</v>
+        <v>21</v>
       </c>
       <c r="AQ201" t="s" s="2">
         <v>21</v>
@@ -28152,10 +28173,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28178,20 +28199,16 @@
         <v>94</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="N202" s="2"/>
+      <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
         <v>21</v>
       </c>
@@ -28215,13 +28232,13 @@
         <v>21</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>21</v>
+        <v>548</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>21</v>
+        <v>549</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>21</v>
@@ -28239,7 +28256,7 @@
         <v>21</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>82</v>
@@ -28254,13 +28271,13 @@
         <v>105</v>
       </c>
       <c r="AK202" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="AL202" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>21</v>
@@ -28269,7 +28286,7 @@
         <v>21</v>
       </c>
       <c r="AP202" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AQ202" t="s" s="2">
         <v>21</v>
@@ -28277,10 +28294,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28297,25 +28314,25 @@
         <v>21</v>
       </c>
       <c r="I203" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J203" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>113</v>
+        <v>253</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>21</v>
@@ -28340,13 +28357,13 @@
         <v>21</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y203" t="s" s="2">
-        <v>568</v>
+        <v>21</v>
       </c>
       <c r="Z203" t="s" s="2">
-        <v>569</v>
+        <v>21</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>21</v>
@@ -28364,7 +28381,7 @@
         <v>21</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>82</v>
@@ -28373,19 +28390,19 @@
         <v>93</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>21</v>
+        <v>551</v>
       </c>
       <c r="AJ203" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>484</v>
+        <v>561</v>
       </c>
       <c r="AN203" t="s" s="2">
         <v>21</v>
@@ -28394,7 +28411,7 @@
         <v>21</v>
       </c>
       <c r="AP203" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="AQ203" t="s" s="2">
         <v>21</v>
@@ -28402,10 +28419,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -28422,24 +28439,26 @@
         <v>21</v>
       </c>
       <c r="I204" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J204" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>574</v>
+        <v>113</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O204" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="O204" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="P204" t="s" s="2">
         <v>21</v>
       </c>
@@ -28463,13 +28482,13 @@
         <v>21</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>21</v>
+        <v>568</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>21</v>
+        <v>569</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>21</v>
@@ -28487,7 +28506,7 @@
         <v>21</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>82</v>
@@ -28502,13 +28521,13 @@
         <v>105</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>21</v>
+        <v>876</v>
       </c>
       <c r="AL204" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>158</v>
+        <v>484</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>21</v>
@@ -28517,7 +28536,7 @@
         <v>21</v>
       </c>
       <c r="AP204" t="s" s="2">
-        <v>158</v>
+        <v>572</v>
       </c>
       <c r="AQ204" t="s" s="2">
         <v>21</v>
@@ -28525,10 +28544,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28551,15 +28570,17 @@
         <v>94</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>196</v>
+        <v>574</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N205" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N205" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
         <v>21</v>
@@ -28608,7 +28629,7 @@
         <v>21</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>82</v>
@@ -28629,7 +28650,7 @@
         <v>21</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>531</v>
+        <v>158</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>21</v>
@@ -28638,7 +28659,7 @@
         <v>21</v>
       </c>
       <c r="AP205" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AQ205" t="s" s="2">
         <v>21</v>
@@ -28646,10 +28667,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28669,23 +28690,19 @@
         <v>21</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>637</v>
+        <v>196</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>638</v>
+        <v>580</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>875</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N206" s="2"/>
+      <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>21</v>
       </c>
@@ -28733,7 +28750,7 @@
         <v>21</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>874</v>
+        <v>582</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>82</v>
@@ -28745,7 +28762,7 @@
         <v>21</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>642</v>
+        <v>105</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>21</v>
@@ -28754,7 +28771,7 @@
         <v>21</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>643</v>
+        <v>531</v>
       </c>
       <c r="AN206" t="s" s="2">
         <v>21</v>
@@ -28763,7 +28780,7 @@
         <v>21</v>
       </c>
       <c r="AP206" t="s" s="2">
-        <v>644</v>
+        <v>138</v>
       </c>
       <c r="AQ206" t="s" s="2">
         <v>21</v>
@@ -28771,10 +28788,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28797,16 +28814,20 @@
         <v>21</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>95</v>
+        <v>637</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>154</v>
+        <v>638</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N207" s="2"/>
-      <c r="O207" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O207" t="s" s="2">
+        <v>880</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>21</v>
       </c>
@@ -28854,7 +28875,7 @@
         <v>21</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>156</v>
+        <v>879</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>82</v>
@@ -28863,10 +28884,10 @@
         <v>93</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>21</v>
+        <v>642</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>21</v>
@@ -28875,7 +28896,7 @@
         <v>21</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>158</v>
+        <v>643</v>
       </c>
       <c r="AN207" t="s" s="2">
         <v>21</v>
@@ -28884,7 +28905,7 @@
         <v>21</v>
       </c>
       <c r="AP207" t="s" s="2">
-        <v>21</v>
+        <v>644</v>
       </c>
       <c r="AQ207" t="s" s="2">
         <v>21</v>
@@ -28892,21 +28913,21 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>21</v>
@@ -28918,17 +28939,15 @@
         <v>21</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>21</v>
@@ -28965,31 +28984,31 @@
         <v>21</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="AC208" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD208" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE208" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>21</v>
@@ -29015,46 +29034,44 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>648</v>
+        <v>162</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>649</v>
+        <v>163</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>21</v>
       </c>
@@ -29066,7 +29083,7 @@
         <v>21</v>
       </c>
       <c r="T209" t="s" s="2">
-        <v>652</v>
+        <v>21</v>
       </c>
       <c r="U209" t="s" s="2">
         <v>21</v>
@@ -29078,52 +29095,52 @@
         <v>21</v>
       </c>
       <c r="X209" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>653</v>
+        <v>21</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>655</v>
+        <v>166</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>879</v>
+        <v>21</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>484</v>
+        <v>158</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>21</v>
@@ -29132,7 +29149,7 @@
         <v>21</v>
       </c>
       <c r="AP209" t="s" s="2">
-        <v>657</v>
+        <v>21</v>
       </c>
       <c r="AQ209" t="s" s="2">
         <v>21</v>
@@ -29140,12 +29157,14 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="C210" s="2"/>
+        <v>882</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>648</v>
+      </c>
       <c r="D210" t="s" s="2">
         <v>21</v>
       </c>
@@ -29163,20 +29182,18 @@
         <v>21</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>113</v>
+        <v>649</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>661</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>21</v>
@@ -29189,7 +29206,7 @@
         <v>21</v>
       </c>
       <c r="T210" t="s" s="2">
-        <v>662</v>
+        <v>21</v>
       </c>
       <c r="U210" t="s" s="2">
         <v>21</v>
@@ -29201,13 +29218,13 @@
         <v>21</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>663</v>
+        <v>21</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>664</v>
+        <v>21</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>21</v>
@@ -29225,19 +29242,19 @@
         <v>21</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>665</v>
+        <v>166</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>21</v>
@@ -29246,7 +29263,7 @@
         <v>21</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>484</v>
+        <v>21</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>21</v>
@@ -29255,7 +29272,7 @@
         <v>21</v>
       </c>
       <c r="AP210" t="s" s="2">
-        <v>666</v>
+        <v>21</v>
       </c>
       <c r="AQ210" t="s" s="2">
         <v>21</v>
@@ -29263,10 +29280,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -29283,25 +29300,25 @@
         <v>21</v>
       </c>
       <c r="I211" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J211" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>670</v>
+        <v>655</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>490</v>
+        <v>656</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>21</v>
@@ -29314,7 +29331,7 @@
         <v>21</v>
       </c>
       <c r="T211" t="s" s="2">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="U211" t="s" s="2">
         <v>21</v>
@@ -29326,13 +29343,13 @@
         <v>21</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>21</v>
+        <v>658</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>21</v>
+        <v>659</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>21</v>
@@ -29350,7 +29367,7 @@
         <v>21</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>82</v>
@@ -29365,13 +29382,13 @@
         <v>105</v>
       </c>
       <c r="AK211" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="AL211" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="AN211" t="s" s="2">
         <v>21</v>
@@ -29380,7 +29397,7 @@
         <v>21</v>
       </c>
       <c r="AP211" t="s" s="2">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="AQ211" t="s" s="2">
         <v>21</v>
@@ -29388,10 +29405,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -29402,7 +29419,7 @@
         <v>82</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>21</v>
@@ -29414,15 +29431,17 @@
         <v>94</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>253</v>
+        <v>113</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>666</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>21</v>
@@ -29435,7 +29454,7 @@
         <v>21</v>
       </c>
       <c r="T212" t="s" s="2">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="U212" t="s" s="2">
         <v>21</v>
@@ -29447,13 +29466,13 @@
         <v>21</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>21</v>
+        <v>668</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>21</v>
+        <v>669</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>21</v>
@@ -29471,13 +29490,13 @@
         <v>21</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>21</v>
@@ -29486,13 +29505,13 @@
         <v>105</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>884</v>
+        <v>21</v>
       </c>
       <c r="AL212" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>681</v>
+        <v>484</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>21</v>
@@ -29501,7 +29520,7 @@
         <v>21</v>
       </c>
       <c r="AP212" t="s" s="2">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="AQ212" t="s" s="2">
         <v>21</v>
@@ -29509,10 +29528,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29532,19 +29551,23 @@
         <v>21</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K213" t="s" s="2">
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>596</v>
+        <v>673</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
+        <v>674</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="O213" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>21</v>
       </c>
@@ -29556,7 +29579,7 @@
         <v>21</v>
       </c>
       <c r="T213" t="s" s="2">
-        <v>21</v>
+        <v>676</v>
       </c>
       <c r="U213" t="s" s="2">
         <v>21</v>
@@ -29592,7 +29615,7 @@
         <v>21</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>156</v>
+        <v>677</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>82</v>
@@ -29604,16 +29627,16 @@
         <v>21</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>21</v>
+        <v>888</v>
       </c>
       <c r="AL213" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>21</v>
+        <v>492</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>21</v>
@@ -29622,7 +29645,7 @@
         <v>21</v>
       </c>
       <c r="AP213" t="s" s="2">
-        <v>21</v>
+        <v>679</v>
       </c>
       <c r="AQ213" t="s" s="2">
         <v>21</v>
@@ -29630,10 +29653,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29653,16 +29676,16 @@
         <v>21</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>141</v>
+        <v>681</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>142</v>
+        <v>682</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -29677,7 +29700,7 @@
         <v>21</v>
       </c>
       <c r="T214" t="s" s="2">
-        <v>21</v>
+        <v>683</v>
       </c>
       <c r="U214" t="s" s="2">
         <v>21</v>
@@ -29701,17 +29724,19 @@
         <v>21</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AC214" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC214" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD214" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>166</v>
+        <v>684</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>82</v>
@@ -29723,16 +29748,16 @@
         <v>21</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="AK214" t="s" s="2">
-        <v>21</v>
+        <v>890</v>
       </c>
       <c r="AL214" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>21</v>
+        <v>686</v>
       </c>
       <c r="AN214" t="s" s="2">
         <v>21</v>
@@ -29741,7 +29766,7 @@
         <v>21</v>
       </c>
       <c r="AP214" t="s" s="2">
-        <v>21</v>
+        <v>687</v>
       </c>
       <c r="AQ214" t="s" s="2">
         <v>21</v>
@@ -29749,14 +29774,12 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>891</v>
+      </c>
+      <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
         <v>21</v>
       </c>
@@ -29777,13 +29800,13 @@
         <v>21</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>687</v>
+        <v>253</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>688</v>
+        <v>596</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>689</v>
+        <v>597</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -29834,19 +29857,19 @@
         <v>21</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>21</v>
@@ -29855,7 +29878,7 @@
         <v>21</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>690</v>
+        <v>21</v>
       </c>
       <c r="AN215" t="s" s="2">
         <v>21</v>
@@ -29872,14 +29895,12 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>692</v>
-      </c>
+        <v>892</v>
+      </c>
+      <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
         <v>21</v>
       </c>
@@ -29888,7 +29909,7 @@
         <v>82</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>21</v>
@@ -29900,13 +29921,13 @@
         <v>21</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>693</v>
+        <v>140</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>694</v>
+        <v>141</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>695</v>
+        <v>142</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -29945,16 +29966,14 @@
         <v>21</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC216" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AC216" s="2"/>
       <c r="AD216" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF216" t="s" s="2">
         <v>166</v>
@@ -29978,7 +29997,7 @@
         <v>21</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>696</v>
+        <v>21</v>
       </c>
       <c r="AN216" t="s" s="2">
         <v>21</v>
@@ -29995,13 +30014,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>21</v>
@@ -30023,13 +30042,13 @@
         <v>21</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -30101,7 +30120,7 @@
         <v>21</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="AN217" t="s" s="2">
         <v>21</v>
@@ -30118,13 +30137,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D218" t="s" s="2">
         <v>21</v>
@@ -30146,13 +30165,13 @@
         <v>21</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -30224,7 +30243,7 @@
         <v>21</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>21</v>
+        <v>701</v>
       </c>
       <c r="AN218" t="s" s="2">
         <v>21</v>
@@ -30241,12 +30260,14 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="C219" s="2"/>
+        <v>892</v>
+      </c>
+      <c r="C219" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="D219" t="s" s="2">
         <v>21</v>
       </c>
@@ -30267,13 +30288,13 @@
         <v>21</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>253</v>
+        <v>704</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -30297,7 +30318,7 @@
         <v>21</v>
       </c>
       <c r="W219" t="s" s="2">
-        <v>710</v>
+        <v>21</v>
       </c>
       <c r="X219" t="s" s="2">
         <v>21</v>
@@ -30324,19 +30345,19 @@
         <v>21</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>606</v>
+        <v>166</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>21</v>
@@ -30345,7 +30366,7 @@
         <v>21</v>
       </c>
       <c r="AM219" t="s" s="2">
-        <v>21</v>
+        <v>706</v>
       </c>
       <c r="AN219" t="s" s="2">
         <v>21</v>
@@ -30362,14 +30383,16 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>892</v>
       </c>
-      <c r="C220" s="2"/>
+      <c r="C220" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="D220" t="s" s="2">
-        <v>712</v>
+        <v>21</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
@@ -30385,16 +30408,16 @@
         <v>21</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>253</v>
+        <v>709</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
@@ -30409,7 +30432,7 @@
         <v>21</v>
       </c>
       <c r="T220" t="s" s="2">
-        <v>715</v>
+        <v>21</v>
       </c>
       <c r="U220" t="s" s="2">
         <v>21</v>
@@ -30445,28 +30468,28 @@
         <v>21</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>716</v>
+        <v>166</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>893</v>
+        <v>21</v>
       </c>
       <c r="AL220" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM220" t="s" s="2">
-        <v>718</v>
+        <v>21</v>
       </c>
       <c r="AN220" t="s" s="2">
         <v>21</v>
@@ -30475,7 +30498,7 @@
         <v>21</v>
       </c>
       <c r="AP220" t="s" s="2">
-        <v>719</v>
+        <v>21</v>
       </c>
       <c r="AQ220" t="s" s="2">
         <v>21</v>
@@ -30483,21 +30506,21 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>721</v>
+        <v>21</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>21</v>
@@ -30506,20 +30529,18 @@
         <v>21</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K221" t="s" s="2">
         <v>253</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N221" t="s" s="2">
-        <v>724</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="N221" s="2"/>
       <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>21</v>
@@ -30532,7 +30553,7 @@
         <v>21</v>
       </c>
       <c r="T221" t="s" s="2">
-        <v>725</v>
+        <v>21</v>
       </c>
       <c r="U221" t="s" s="2">
         <v>21</v>
@@ -30541,7 +30562,7 @@
         <v>21</v>
       </c>
       <c r="W221" t="s" s="2">
-        <v>21</v>
+        <v>715</v>
       </c>
       <c r="X221" t="s" s="2">
         <v>21</v>
@@ -30568,7 +30589,7 @@
         <v>21</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>726</v>
+        <v>606</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>82</v>
@@ -30580,7 +30601,7 @@
         <v>21</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>21</v>
@@ -30589,7 +30610,7 @@
         <v>21</v>
       </c>
       <c r="AM221" t="s" s="2">
-        <v>727</v>
+        <v>21</v>
       </c>
       <c r="AN221" t="s" s="2">
         <v>21</v>
@@ -30598,7 +30619,7 @@
         <v>21</v>
       </c>
       <c r="AP221" t="s" s="2">
-        <v>728</v>
+        <v>21</v>
       </c>
       <c r="AQ221" t="s" s="2">
         <v>21</v>
@@ -30606,14 +30627,14 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
@@ -30635,10 +30656,10 @@
         <v>253</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -30653,7 +30674,7 @@
         <v>21</v>
       </c>
       <c r="T222" t="s" s="2">
-        <v>21</v>
+        <v>720</v>
       </c>
       <c r="U222" t="s" s="2">
         <v>21</v>
@@ -30689,7 +30710,7 @@
         <v>21</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>82</v>
@@ -30704,13 +30725,13 @@
         <v>105</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="AL222" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>21</v>
@@ -30719,7 +30740,7 @@
         <v>21</v>
       </c>
       <c r="AP222" t="s" s="2">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="AQ222" t="s" s="2">
         <v>21</v>
@@ -30727,21 +30748,21 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H223" t="s" s="2">
         <v>21</v>
@@ -30756,12 +30777,14 @@
         <v>253</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N223" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="N223" t="s" s="2">
+        <v>729</v>
+      </c>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
         <v>21</v>
@@ -30774,7 +30797,7 @@
         <v>21</v>
       </c>
       <c r="T223" t="s" s="2">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="U223" t="s" s="2">
         <v>21</v>
@@ -30810,7 +30833,7 @@
         <v>21</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>82</v>
@@ -30825,13 +30848,13 @@
         <v>105</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>898</v>
+        <v>21</v>
       </c>
       <c r="AL223" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="AN223" t="s" s="2">
         <v>21</v>
@@ -30840,7 +30863,7 @@
         <v>21</v>
       </c>
       <c r="AP223" t="s" s="2">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="AQ223" t="s" s="2">
         <v>21</v>
@@ -30848,14 +30871,14 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>21</v>
+        <v>735</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
@@ -30877,14 +30900,12 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>749</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="N224" s="2"/>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
         <v>21</v>
@@ -30933,7 +30954,7 @@
         <v>21</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>82</v>
@@ -30948,13 +30969,13 @@
         <v>105</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="AN224" t="s" s="2">
         <v>21</v>
@@ -30963,7 +30984,7 @@
         <v>21</v>
       </c>
       <c r="AP224" t="s" s="2">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="AQ224" t="s" s="2">
         <v>21</v>
@@ -30971,21 +30992,21 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
-        <v>21</v>
+        <v>743</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>21</v>
@@ -30997,18 +31018,16 @@
         <v>94</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="N225" s="2"/>
-      <c r="O225" t="s" s="2">
-        <v>757</v>
-      </c>
+      <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>21</v>
       </c>
@@ -31020,7 +31039,7 @@
         <v>21</v>
       </c>
       <c r="T225" t="s" s="2">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="U225" t="s" s="2">
         <v>21</v>
@@ -31056,7 +31075,7 @@
         <v>21</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>82</v>
@@ -31071,13 +31090,13 @@
         <v>105</v>
       </c>
       <c r="AK225" t="s" s="2">
-        <v>21</v>
+        <v>904</v>
       </c>
       <c r="AL225" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>531</v>
+        <v>749</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>21</v>
@@ -31086,7 +31105,7 @@
         <v>21</v>
       </c>
       <c r="AP225" t="s" s="2">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="AQ225" t="s" s="2">
         <v>21</v>
@@ -31094,10 +31113,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -31117,21 +31136,21 @@
         <v>21</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>113</v>
+        <v>253</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>584</v>
+        <v>752</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="N226" s="2"/>
-      <c r="O226" t="s" s="2">
-        <v>904</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>21</v>
       </c>
@@ -31155,13 +31174,13 @@
         <v>21</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>588</v>
+        <v>21</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>589</v>
+        <v>21</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>21</v>
@@ -31179,7 +31198,7 @@
         <v>21</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>902</v>
+        <v>755</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>82</v>
@@ -31194,22 +31213,22 @@
         <v>105</v>
       </c>
       <c r="AK226" t="s" s="2">
-        <v>158</v>
+        <v>906</v>
       </c>
       <c r="AL226" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>591</v>
+        <v>757</v>
       </c>
       <c r="AN226" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO226" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP226" t="s" s="2">
-        <v>905</v>
+        <v>758</v>
       </c>
       <c r="AQ226" t="s" s="2">
         <v>21</v>
@@ -31217,10 +31236,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -31231,7 +31250,7 @@
         <v>82</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H227" t="s" s="2">
         <v>21</v>
@@ -31240,19 +31259,21 @@
         <v>21</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>596</v>
+        <v>760</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>597</v>
+        <v>761</v>
       </c>
       <c r="N227" s="2"/>
-      <c r="O227" s="2"/>
+      <c r="O227" t="s" s="2">
+        <v>762</v>
+      </c>
       <c r="P227" t="s" s="2">
         <v>21</v>
       </c>
@@ -31264,7 +31285,7 @@
         <v>21</v>
       </c>
       <c r="T227" t="s" s="2">
-        <v>21</v>
+        <v>763</v>
       </c>
       <c r="U227" t="s" s="2">
         <v>21</v>
@@ -31300,7 +31321,7 @@
         <v>21</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>156</v>
+        <v>764</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>82</v>
@@ -31312,7 +31333,7 @@
         <v>21</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK227" t="s" s="2">
         <v>21</v>
@@ -31321,7 +31342,7 @@
         <v>21</v>
       </c>
       <c r="AM227" t="s" s="2">
-        <v>21</v>
+        <v>531</v>
       </c>
       <c r="AN227" t="s" s="2">
         <v>21</v>
@@ -31330,7 +31351,7 @@
         <v>21</v>
       </c>
       <c r="AP227" t="s" s="2">
-        <v>21</v>
+        <v>765</v>
       </c>
       <c r="AQ227" t="s" s="2">
         <v>21</v>
@@ -31338,10 +31359,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -31352,7 +31373,7 @@
         <v>82</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>21</v>
@@ -31364,16 +31385,18 @@
         <v>21</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>141</v>
+        <v>584</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>142</v>
+        <v>909</v>
       </c>
       <c r="N228" s="2"/>
-      <c r="O228" s="2"/>
+      <c r="O228" t="s" s="2">
+        <v>910</v>
+      </c>
       <c r="P228" t="s" s="2">
         <v>21</v>
       </c>
@@ -31397,59 +31420,61 @@
         <v>21</v>
       </c>
       <c r="X228" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>21</v>
+        <v>588</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>21</v>
+        <v>589</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB228" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AC228" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC228" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE228" t="s" s="2">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>166</v>
+        <v>908</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AL228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM228" t="s" s="2">
-        <v>21</v>
+        <v>591</v>
       </c>
       <c r="AN228" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO228" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AP228" t="s" s="2">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="AQ228" t="s" s="2">
         <v>21</v>
@@ -31457,14 +31482,12 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
         <v>21</v>
       </c>
@@ -31485,13 +31508,13 @@
         <v>21</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>601</v>
+        <v>253</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -31542,19 +31565,19 @@
         <v>21</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK229" t="s" s="2">
         <v>21</v>
@@ -31580,10 +31603,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31594,7 +31617,7 @@
         <v>82</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>21</v>
@@ -31606,13 +31629,13 @@
         <v>21</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>605</v>
+        <v>141</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>605</v>
+        <v>142</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -31651,31 +31674,29 @@
         <v>21</v>
       </c>
       <c r="AB230" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AC230" s="2"/>
       <c r="AD230" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE230" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>606</v>
+        <v>166</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="AK230" t="s" s="2">
         <v>21</v>
@@ -31701,12 +31722,14 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>910</v>
-      </c>
-      <c r="C231" s="2"/>
+        <v>913</v>
+      </c>
+      <c r="C231" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="D231" t="s" s="2">
         <v>21</v>
       </c>
@@ -31727,18 +31750,16 @@
         <v>21</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>269</v>
+        <v>601</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>911</v>
+        <v>602</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>912</v>
+        <v>603</v>
       </c>
       <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>913</v>
-      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>21</v>
       </c>
@@ -31786,37 +31807,37 @@
         <v>21</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>910</v>
+        <v>166</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>846</v>
+        <v>21</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK231" t="s" s="2">
-        <v>914</v>
+        <v>21</v>
       </c>
       <c r="AL231" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>915</v>
+        <v>21</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP231" t="s" s="2">
-        <v>916</v>
+        <v>21</v>
       </c>
       <c r="AQ231" t="s" s="2">
         <v>21</v>
@@ -31824,10 +31845,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31850,13 +31871,13 @@
         <v>21</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>918</v>
+        <v>605</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>919</v>
+        <v>605</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
@@ -31907,7 +31928,7 @@
         <v>21</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>917</v>
+        <v>606</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>82</v>
@@ -31919,22 +31940,22 @@
         <v>21</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AL232" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM232" t="s" s="2">
-        <v>920</v>
+        <v>21</v>
       </c>
       <c r="AN232" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>21</v>
@@ -31945,10 +31966,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -31959,7 +31980,7 @@
         <v>82</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>21</v>
@@ -31971,19 +31992,17 @@
         <v>21</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>807</v>
+        <v>269</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>924</v>
-      </c>
+        <v>918</v>
+      </c>
+      <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>21</v>
@@ -32032,37 +32051,37 @@
         <v>21</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>21</v>
+        <v>851</v>
       </c>
       <c r="AJ233" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>21</v>
+        <v>920</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM233" t="s" s="2">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="AN233" t="s" s="2">
-        <v>927</v>
+        <v>21</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>928</v>
+        <v>158</v>
       </c>
       <c r="AP233" t="s" s="2">
-        <v>21</v>
+        <v>922</v>
       </c>
       <c r="AQ233" t="s" s="2">
         <v>21</v>
@@ -32070,10 +32089,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -32096,13 +32115,13 @@
         <v>21</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>154</v>
+        <v>924</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>155</v>
+        <v>925</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -32153,7 +32172,7 @@
         <v>21</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>156</v>
+        <v>923</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>82</v>
@@ -32162,25 +32181,25 @@
         <v>93</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM234" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="AN234" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO234" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AN234" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO234" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AP234" t="s" s="2">
         <v>21</v>
@@ -32191,14 +32210,14 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
@@ -32217,18 +32236,20 @@
         <v>21</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>140</v>
+        <v>812</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>162</v>
+        <v>928</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>163</v>
+        <v>929</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O235" s="2"/>
+        <v>930</v>
+      </c>
+      <c r="O235" t="s" s="2">
+        <v>931</v>
+      </c>
       <c r="P235" t="s" s="2">
         <v>21</v>
       </c>
@@ -32276,7 +32297,7 @@
         <v>21</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>166</v>
+        <v>927</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>82</v>
@@ -32288,7 +32309,7 @@
         <v>21</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="AK235" t="s" s="2">
         <v>21</v>
@@ -32297,13 +32318,13 @@
         <v>21</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>158</v>
+        <v>932</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>21</v>
+        <v>933</v>
       </c>
       <c r="AO235" t="s" s="2">
-        <v>21</v>
+        <v>934</v>
       </c>
       <c r="AP235" t="s" s="2">
         <v>21</v>
@@ -32314,46 +32335,42 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
-        <v>817</v>
+        <v>21</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I236" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J236" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>818</v>
+        <v>154</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>21</v>
       </c>
@@ -32401,19 +32418,19 @@
         <v>21</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>820</v>
+        <v>156</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK236" t="s" s="2">
         <v>21</v>
@@ -32422,7 +32439,7 @@
         <v>21</v>
       </c>
       <c r="AM236" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AN236" t="s" s="2">
         <v>21</v>
@@ -32439,21 +32456,21 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>21</v>
@@ -32465,20 +32482,18 @@
         <v>21</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>933</v>
+        <v>162</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>934</v>
+        <v>163</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>936</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="O237" s="2"/>
       <c r="P237" t="s" s="2">
         <v>21</v>
       </c>
@@ -32502,13 +32517,13 @@
         <v>21</v>
       </c>
       <c r="X237" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AA237" t="s" s="2">
         <v>21</v>
@@ -32526,37 +32541,37 @@
         <v>21</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>932</v>
+        <v>166</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK237" t="s" s="2">
-        <v>937</v>
+        <v>21</v>
       </c>
       <c r="AL237" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM237" t="s" s="2">
-        <v>938</v>
+        <v>158</v>
       </c>
       <c r="AN237" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO237" t="s" s="2">
-        <v>939</v>
+        <v>21</v>
       </c>
       <c r="AP237" t="s" s="2">
-        <v>940</v>
+        <v>21</v>
       </c>
       <c r="AQ237" t="s" s="2">
         <v>21</v>
@@ -32564,45 +32579,45 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
-        <v>21</v>
+        <v>822</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I238" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J238" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>338</v>
+        <v>140</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>942</v>
+        <v>823</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>943</v>
+        <v>824</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>944</v>
+        <v>164</v>
       </c>
       <c r="O238" t="s" s="2">
-        <v>945</v>
+        <v>211</v>
       </c>
       <c r="P238" t="s" s="2">
         <v>21</v>
@@ -32651,37 +32666,37 @@
         <v>21</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>941</v>
+        <v>825</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK238" t="s" s="2">
-        <v>946</v>
+        <v>21</v>
       </c>
       <c r="AL238" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>947</v>
+        <v>138</v>
       </c>
       <c r="AN238" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO238" t="s" s="2">
-        <v>948</v>
+        <v>21</v>
       </c>
       <c r="AP238" t="s" s="2">
-        <v>949</v>
+        <v>21</v>
       </c>
       <c r="AQ238" t="s" s="2">
         <v>21</v>
@@ -32689,21 +32704,21 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>951</v>
+        <v>21</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>21</v>
@@ -32715,18 +32730,20 @@
         <v>21</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>952</v>
+        <v>181</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>953</v>
+        <v>939</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="O239" s="2"/>
+        <v>941</v>
+      </c>
+      <c r="O239" t="s" s="2">
+        <v>942</v>
+      </c>
       <c r="P239" t="s" s="2">
         <v>21</v>
       </c>
@@ -32750,13 +32767,13 @@
         <v>21</v>
       </c>
       <c r="X239" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="Y239" t="s" s="2">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="Z239" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AA239" t="s" s="2">
         <v>21</v>
@@ -32774,13 +32791,13 @@
         <v>21</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI239" t="s" s="2">
         <v>21</v>
@@ -32789,22 +32806,22 @@
         <v>105</v>
       </c>
       <c r="AK239" t="s" s="2">
-        <v>956</v>
+        <v>943</v>
       </c>
       <c r="AL239" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO239" t="s" s="2">
-        <v>158</v>
+        <v>945</v>
       </c>
       <c r="AP239" t="s" s="2">
-        <v>958</v>
+        <v>946</v>
       </c>
       <c r="AQ239" t="s" s="2">
         <v>21</v>
@@ -32812,10 +32829,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -32835,22 +32852,22 @@
         <v>21</v>
       </c>
       <c r="J240" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>269</v>
+        <v>338</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="O240" t="s" s="2">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="P240" t="s" s="2">
         <v>21</v>
@@ -32899,7 +32916,7 @@
         <v>21</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>82</v>
@@ -32914,22 +32931,22 @@
         <v>105</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="AL240" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>915</v>
+        <v>953</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO240" t="s" s="2">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="AP240" t="s" s="2">
-        <v>21</v>
+        <v>955</v>
       </c>
       <c r="AQ240" t="s" s="2">
         <v>21</v>
@@ -32937,14 +32954,14 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
-        <v>21</v>
+        <v>957</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
@@ -32957,26 +32974,24 @@
         <v>21</v>
       </c>
       <c r="I241" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>807</v>
+        <v>958</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="N241" t="s" s="2">
-        <v>969</v>
-      </c>
-      <c r="O241" t="s" s="2">
-        <v>970</v>
-      </c>
+        <v>961</v>
+      </c>
+      <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>21</v>
       </c>
@@ -33024,7 +33039,7 @@
         <v>21</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>82</v>
@@ -33039,13 +33054,13 @@
         <v>105</v>
       </c>
       <c r="AK241" t="s" s="2">
-        <v>21</v>
+        <v>962</v>
       </c>
       <c r="AL241" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="AN241" t="s" s="2">
         <v>21</v>
@@ -33054,7 +33069,7 @@
         <v>158</v>
       </c>
       <c r="AP241" t="s" s="2">
-        <v>21</v>
+        <v>964</v>
       </c>
       <c r="AQ241" t="s" s="2">
         <v>21</v>
@@ -33062,10 +33077,10 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -33085,19 +33100,23 @@
         <v>21</v>
       </c>
       <c r="J242" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>154</v>
+        <v>966</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N242" s="2"/>
-      <c r="O242" s="2"/>
+        <v>967</v>
+      </c>
+      <c r="N242" t="s" s="2">
+        <v>968</v>
+      </c>
+      <c r="O242" t="s" s="2">
+        <v>969</v>
+      </c>
       <c r="P242" t="s" s="2">
         <v>21</v>
       </c>
@@ -33145,7 +33164,7 @@
         <v>21</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>156</v>
+        <v>965</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>82</v>
@@ -33154,25 +33173,25 @@
         <v>93</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AK242" t="s" s="2">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AL242" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>158</v>
+        <v>921</v>
       </c>
       <c r="AN242" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO242" t="s" s="2">
-        <v>21</v>
+        <v>971</v>
       </c>
       <c r="AP242" t="s" s="2">
         <v>21</v>
@@ -33183,14 +33202,14 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
@@ -33203,24 +33222,26 @@
         <v>21</v>
       </c>
       <c r="I243" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J243" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>140</v>
+        <v>812</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>162</v>
+        <v>973</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>163</v>
+        <v>974</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O243" s="2"/>
+        <v>975</v>
+      </c>
+      <c r="O243" t="s" s="2">
+        <v>976</v>
+      </c>
       <c r="P243" t="s" s="2">
         <v>21</v>
       </c>
@@ -33268,7 +33289,7 @@
         <v>21</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>166</v>
+        <v>972</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>82</v>
@@ -33280,7 +33301,7 @@
         <v>21</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="AK243" t="s" s="2">
         <v>21</v>
@@ -33289,13 +33310,13 @@
         <v>21</v>
       </c>
       <c r="AM243" t="s" s="2">
+        <v>977</v>
+      </c>
+      <c r="AN243" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO243" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AP243" t="s" s="2">
         <v>21</v>
@@ -33306,46 +33327,42 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
-        <v>817</v>
+        <v>21</v>
       </c>
       <c r="E244" s="2"/>
       <c r="F244" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I244" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="J244" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>818</v>
+        <v>154</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="N244" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O244" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N244" s="2"/>
+      <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
         <v>21</v>
       </c>
@@ -33393,19 +33410,19 @@
         <v>21</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>820</v>
+        <v>156</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="AK244" t="s" s="2">
         <v>21</v>
@@ -33414,7 +33431,7 @@
         <v>21</v>
       </c>
       <c r="AM244" t="s" s="2">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="AN244" t="s" s="2">
         <v>21</v>
@@ -33431,21 +33448,21 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>21</v>
@@ -33454,19 +33471,19 @@
         <v>21</v>
       </c>
       <c r="J245" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>976</v>
+        <v>140</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>977</v>
+        <v>162</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>968</v>
+        <v>163</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>978</v>
+        <v>164</v>
       </c>
       <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
@@ -33516,37 +33533,37 @@
         <v>21</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>975</v>
+        <v>166</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH245" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI245" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ245" t="s" s="2">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="AK245" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL245" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM245" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AL245" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM245" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="AN245" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO245" t="s" s="2">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="AP245" t="s" s="2">
-        <v>979</v>
+        <v>21</v>
       </c>
       <c r="AQ245" t="s" s="2">
         <v>21</v>
@@ -33561,35 +33578,39 @@
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
-        <v>21</v>
+        <v>822</v>
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H246" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I246" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="J246" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>981</v>
+        <v>823</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>982</v>
-      </c>
-      <c r="N246" s="2"/>
-      <c r="O246" s="2"/>
+        <v>824</v>
+      </c>
+      <c r="N246" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O246" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P246" t="s" s="2">
         <v>21</v>
       </c>
@@ -33613,63 +33634,307 @@
         <v>21</v>
       </c>
       <c r="X246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF246" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="AG246" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH246" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ246" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM246" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AN246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP246" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AQ246" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E247" s="2"/>
+      <c r="F247" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G247" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J247" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K247" t="s" s="2">
+        <v>982</v>
+      </c>
+      <c r="L247" t="s" s="2">
+        <v>983</v>
+      </c>
+      <c r="M247" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="N247" t="s" s="2">
+        <v>984</v>
+      </c>
+      <c r="O247" s="2"/>
+      <c r="P247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q247" s="2"/>
+      <c r="R247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF247" t="s" s="2">
+        <v>981</v>
+      </c>
+      <c r="AG247" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH247" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ247" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK247" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM247" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AN247" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO247" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AP247" t="s" s="2">
+        <v>985</v>
+      </c>
+      <c r="AQ247" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E248" s="2"/>
+      <c r="F248" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G248" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J248" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K248" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L248" t="s" s="2">
+        <v>987</v>
+      </c>
+      <c r="M248" t="s" s="2">
+        <v>988</v>
+      </c>
+      <c r="N248" s="2"/>
+      <c r="O248" s="2"/>
+      <c r="P248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q248" s="2"/>
+      <c r="R248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X248" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y246" t="s" s="2">
-        <v>983</v>
-      </c>
-      <c r="Z246" t="s" s="2">
-        <v>984</v>
-      </c>
-      <c r="AA246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF246" t="s" s="2">
-        <v>980</v>
-      </c>
-      <c r="AG246" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH246" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ246" t="s" s="2">
+      <c r="Y248" t="s" s="2">
+        <v>989</v>
+      </c>
+      <c r="Z248" t="s" s="2">
+        <v>990</v>
+      </c>
+      <c r="AA248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF248" t="s" s="2">
+        <v>986</v>
+      </c>
+      <c r="AG248" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH248" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ248" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK246" t="s" s="2">
+      <c r="AK248" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AL246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM246" t="s" s="2">
-        <v>985</v>
-      </c>
-      <c r="AN246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO246" t="s" s="2">
+      <c r="AL248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM248" t="s" s="2">
+        <v>991</v>
+      </c>
+      <c r="AN248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO248" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AP246" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AQ246" t="s" s="2">
+      <c r="AP248" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AQ248" t="s" s="2">
         <v>21</v>
       </c>
     </row>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T14:33:31+00:00</t>
+    <t>2024-10-30T15:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T15:48:47+00:00</t>
+    <t>2024-11-17T20:47:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:47:41+00:00</t>
+    <t>2024-11-17T21:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:35:06+00:00</t>
+    <t>2024-11-27T13:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:18:58+00:00</t>
+    <t>2024-12-15T14:03:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T14:03:14+00:00</t>
+    <t>2024-12-19T08:32:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T14:32:12+00:00</t>
+    <t>2025-01-24T13:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T13:05:30+00:00</t>
+    <t>2025-01-24T15:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:13:16+00:00</t>
+    <t>2025-01-27T12:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T09:10:20+00:00</t>
+    <t>2026-03-01T19:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r5-core-main/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:31:53+00:00</t>
+    <t>2026-07-17T05:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
